--- a/Result/checksun_type/油空壓元件.xlsx
+++ b/Result/checksun_type/油空壓元件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>496.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>557.67</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>475.1</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>557.67</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>475.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2750222675.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1447134942.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1447134942.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1053597321.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2152581308.02</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2152581308.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-33699424.8007679</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2750222675</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2750222675.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>494.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>562.72</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>472.03</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>562.72</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>472.03</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3390325071.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>994031621.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>994031621.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>898144693.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2147035688.04</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2147035688.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-160043998.1462588</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3390325071</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3390325071.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>483.2</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>563.92</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>468.36</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>563.92</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>468.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>459299671.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>450126458.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>450126458</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>671940209.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2096190446.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2096190446.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-403402788.2774504</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>459299671</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>459299671.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>491.6</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>566.67</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>465.54</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>566.67</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>465.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>365918659.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>434925730.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>434925730.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1021043203.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2104434879.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2104434879.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-422612524.5978156</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>365918659</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>365918659.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>499.1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>568.83</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>463.16</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>568.83</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>463.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>269908638.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>513473568.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>513473568.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1315445895.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2119212794.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2119212794.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-424956592.1769866</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>269908638</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>269908638.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>507.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>569.17</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>459.6</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>569.17</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>459.6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>484706069.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>660059701.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>660059701</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1713834804.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2131373509.86</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2131373509.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-402841451.0337672</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>484706069</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>484706069.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>512.9</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>570.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>456.27</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>570.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>456.27</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>670799253.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>802257765.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>802257765.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2014584708.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2148716890.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2148716890.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-379875208.0422475</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>670799253</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>670799253.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>535.1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>573.48</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>453.57</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>573.48</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>453.57</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>383296034.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>893753960.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>893753960.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2546631507.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2180684277.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2180684277.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-353437873.1957107</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>383296034</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>383296034.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>555.7</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>574.62</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>450.31</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>574.62</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>450.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>758657848.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1607160676.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1607160676.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2641723014.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2202777144.4</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2202777144.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-272243554.4793825</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>758657848</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>758657848.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>580.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>577.15</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>447.66</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>577.15</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>447.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1002839301.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2117418222.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>2117418222.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2677703348.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2224419074.7</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2224419074.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-186746023.7246504</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1002839301</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1002839301.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>601.6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>574.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>444.3</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>574.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>444.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1195696393.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2767609907.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2767609907.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2765901465.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2231040193.68</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2231040193.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-84099491.76343775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1195696393</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1195696393.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>49.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>50.81</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>52.38</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>52.38</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>399.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-18.18075394159126</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>399</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.6</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>50.94</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>52.49</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>52.49</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-15.0438635940464</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>49</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>49.46999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>51.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>52.63</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>52.63</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>0</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>49.47</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>52.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>52.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>0</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>49.52999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>52.83</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>52.83</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>0</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>49.77</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>51.64</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>52.94</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>954.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>832.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>832.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>599.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>954</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>954.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>51.85</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>53.03</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>53.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>302.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>827.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>827.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>79.69718450726532</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>302</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>302.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>51.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>52.14</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>53.15</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>53.15</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>422.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>866.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>866.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>122.8318633911232</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>422</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>422.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>51.46</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>52.26</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>53.21</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>53.21</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2176.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>796.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>796.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>167.2088381040944</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2176</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2176.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>51.77999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>53.28</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>53.28</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>309.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>375.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>375.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>36.70420061890684</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>309</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>51.92</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>52.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>53.34</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>53.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>928.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>365.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>365.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>48.99385418939238</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>928</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>42.7</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>42.49</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>42.87</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>130.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-25.87701673377518</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>130</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>42.63</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>42.42</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>42.89</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>42.89</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-18.13077200027095</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>0</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>42.65</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>42.37</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>42.92</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>42.92</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>290.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-18.13077200027095</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>290</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>42.33</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>42.97</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>42.97</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>164.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-26.58331393249824</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>164</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>42.48</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>42.26</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>43.02</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>43.02</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>8.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-24.20896976666228</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>8</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>42.48</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>43.06</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>43.06</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>17.79539670234334</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>0</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>42.48</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>42.19</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>17.79539670234334</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>0</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>42.37</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>42.18</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>43.17</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>43.17</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>333.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>333.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>245.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>17.79539670234334</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>601</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>601.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>42.22</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>42.17</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>461.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>215.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>215.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>250.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-9.226211371127249</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>461</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>42.19</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>43.25</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>94.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>140</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>216.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-32.49900106997356</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>94</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>42.18</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>42.19</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>43.29</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>301.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>249.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>249.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>240.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-25.26373631582641</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>301</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>301.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>40.95</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>42.64</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2421847.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>3791179.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>3791179.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>8441913.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>18144900.44</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>18144900.44</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-2601451.757577688</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2421847</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2421847.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.81</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>42.74</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>43.82</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>43.82</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>4728331.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>4640603.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>4640603.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>10531808.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>18981238.56</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>18981238.56</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-2490410.871163477</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>4728331</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>4728331.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>40.88</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>42.91</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>43.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>3412251.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5288830.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5288830.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>13621042.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>19455359.98</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>19455359.98</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2489961.07374448</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>3412251</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>3412251.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>43.17</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>43.99</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>43.99</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>6222251.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>6831106.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>6831106.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>14290454.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>20206651.98</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>20206651.98</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-2259382.753369324</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>6222251</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>6222251.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>41.88</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>44.09</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>44.09</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>2171218.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>7709357.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>7709357.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>15585941.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>21466838.98</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>21466838.98</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-2150364.340213053</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2171218</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2171218.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>42.45</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>43.61</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>44.18</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>44.18</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>6668966.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>13092646.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>13092646.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>16658270.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>22433638.84</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>22433638.84</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-1483785.773553628</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>6668966</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>6668966.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>43.84</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>44.26</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>7969466.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>16423013.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>16423013.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>16879569.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>23757455.1</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>23757455.1</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-960439.9006989673</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>7969466</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>7969466.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>44.45</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>11123632.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>21953254.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>21953254.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>16943505.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>24891638.16</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>24891638.16</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-317840.8001673408</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>11123632</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>11123632.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>44.9</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>44.11</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>44.48</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>44.48</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>10613505.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>21749802.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>21749802.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>16553691.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>29980160.82</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>29980160.82</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>273563.01488382</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>10613505</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>10613505.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>45.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>44.63</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>44.63</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>29087663.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>23462526.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>23462526.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>16209059.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>40577803.06</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>40577803.06</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>1163311.96442534</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>29087663</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>29087663.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>44.79</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>44.73</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>44.73</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>23320800.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>20223895.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>20223895.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>14247583.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>46935147.28</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>46935147.28</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>413460.9650408886</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>23320800</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>23320800.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.14</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>40.34</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>40.88</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>40.88</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1008.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>58.77026642390729</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1008</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1008.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>40.35</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2.954113860118895</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>159</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>40.21</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>40.99</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>40.99</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>0</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>40.18</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>40.44</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>145.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>208.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>208.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>198.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>145</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>40.08</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>40.48</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>41.04</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>195.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>215.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>215.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>192.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>7.197985201104501</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>195</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>39.76</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>40.42</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>508.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>176.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>176.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>197.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>10.18135394838995</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>508</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>508.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>39.71</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>118.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>118.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>162.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-19.4560247679305</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>156</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>39.91</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>40.52</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>41.1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>164</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-23.38599347810501</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>40</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>40.61</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>178.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>188.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>188.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-15.73644901127915</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>178</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>40.60000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>40.73</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>169.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>169.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-19.03222659398224</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>40.68000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>40.82</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>41.19</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>41.19</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>217.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>217.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>217.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>0</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4.203615048058737</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>217</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
